--- a/content/tz-shkola-kitayskogo-yazyka-v-moskve.xlsx
+++ b/content/tz-shkola-kitayskogo-yazyka-v-moskve.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>выбор школы китайского в Москве: полная цена занятия вместе с дорогой, кому нужен офлайн, вопросы про расписание</t>
+          <t>выбор школы китайского в Москве: сколько времени занимает урок вместе с дорогой, кому нужны очные занятия, о чём спросить школу</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Школа китайского языка в Москве: что считать перед выбором, кроме цены занятия</t>
+          <t>Школа китайского языка в Москве: что посчитать, кроме цены занятия</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Школа китайского языка в Москве выбирается не по цене занятия. В большом городе к каждому уроку прибавляется дорога, и вечер уходит целиком — а рушит регулярность чаще всего именно она, а не сложность языка. Разбираем, как считать полную цену занятия вместе с дорогой, кому офлайн всё-таки нужнее и что спросить про перенос, заморозку и замену преподавателя. И честно говорим, что своего офиса в Москве у нас нет: мы онлайн-школа.</t>
+          <t>Школа китайского языка в Москве выбирается не по цене занятия. К каждому уроку в большом городе добавляется дорога, и на занятие уходит весь вечер. Чаще всего люди бросают китайский именно из-за дороги, а не из-за того, что язык сложный. Разбираем, как посчитать, сколько времени на самом деле стоит вам один урок, кому очные занятия правда нужнее и о чём спросить школу до оплаты. И честно говорим, что офиса в Москве у нас нет: мы онлайн-школа.</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Почему школу китайского в Москве выбирают не по цене занятия, как считать время двери-в-дверь, кому офлайн нужнее и что спросить про перенос и заморозку занятий.</t>
+          <t>Почему школу китайского в Москве стоит выбирать не по цене занятия, как посчитать время вместе с дорогой, кому нужны очные занятия и о чём спросить школу до оплаты.</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>37 194 знака (лимит ≈ 50 000)</t>
+          <t>37 497 знаков (лимит ≈ 50 000)</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>26,1 % (норма 26–31 %)</t>
+          <t>26,6 % (норма 26–31 %)</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>35,9 %; FAQ на 59,2 %</t>
+          <t>36,7 %; FAQ на 59,4 %</t>
         </is>
       </c>
     </row>
@@ -713,24 +713,24 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>полной цене занятия</t>
+          <t>тому, во что урок обходится на самом деле</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Полная цена занятия</t>
+          <t>Время на один урок</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>включает</t>
+          <t>складывается из</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>дорогу туда и обратно</t>
+          <t>дороги туда, урока и дороги обратно</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Регулярность</t>
+          <t>Формат</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>решает</t>
+          <t>значит меньше, чем</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>больше, чем формат</t>
+          <t>то, дойдёте ли вы до занятия</t>
         </is>
       </c>
     </row>
@@ -1331,18 +1331,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Падежи и язык</t>
+          <t>Падежи, язык и большой проход после первой сдачи</t>
         </is>
       </c>
     </row>
@@ -1366,49 +1366,219 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>«в статьях про КИТАЙСКОМ ЯЗЫКЕ для детей»</t>
+          <t>«ВРЕМЯ ДВЕРИ-В-ДВЕРЬ» — тайтл, дескрипшен, H2, паспорт, боковая заметка, FAQ (6 мест)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>«в статьях про китайский язык для детей»</t>
+          <t>«время вместе с дорогой»</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>СЛОМАННЫЙ ПАДЕЖ. Заведён отдельный вариант подписи в винительном</t>
+          <t>ЗАКАЗЧИК: трудно читать. Выражение звучит как термин из логистики, а не как обычная речь</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>«в разборе про ГРУППОВЫХ ЗАНЯТИЯХ по китайскому языку»</t>
+          <t>«Офлайн честно нужнее в трёх случаях — дома не сосредоточиться, без внешней дисциплины вы не сядете, и маленький ребёнок»</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>«в разборе про групповые занятия по китайскому языку»</t>
+          <t>«Очные занятия правда лучше в трёх случаях: дома не получается сосредоточиться; сами за урок вы не сядете; ребёнку ещё мало лет»</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>СЛОМАННЫЙ ПАДЕЖ. Заведён отдельный вариант подписи в винительном</t>
+          <t>Перечисление было свёрнуто в обрывки. Развёрнуто в нормальные предложения</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>«перенос, заморозка на отпуск, замена заболевшего преподавателя»</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>«можно ли перенести занятие, что будет с оплатой, если вы уедете, и кто проведёт урок, если преподаватель заболел»</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Три существительных подряд вместо вопросов. Переписано глаголами</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>«И регулярность решает больше формата»</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>«И важнее всего не формат, а то, дойдёте ли вы»</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Свёрнутая формулировка</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>«в часах, которых у вас не будет ни на что другое»</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>«Вот сколько времени на самом деле стоит вам один урок»</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Закручено</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>«Если за месяц из восьми занятий вы доехали до шести, то каждый состоявшийся урок обошёлся вам на треть дороже»</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>«Допустим, за месяц вы были на шести занятиях из восьми. Значит, каждое занятие, на котором вы были, обошлось вам дороже, чем написано в прайсе»</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Длинное условное предложение с подсчётом внутри. Разбито на два и убрана лишняя дробь</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>«сходится ли у вас арифметика вечера» (CTA)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>«посчитать вместе, сколько времени у вас займут занятия»</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>«Арифметика вечера» — красивая, но непонятная фраза</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>«Дело не в возрасте как таковом, а в том, сколько ребёнок выдерживает экран»</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>«Дело не в самом возрасте, а в том, сколько ребёнок может сидеть перед экраном»</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>«Как таковом» и «выдерживает экран» — книжное</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>«материал успевает выветриться между уроками»</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>«за семь дней успеваешь забыть то, что было на прошлом уроке»</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Метафора вместо обычного глагола</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ПРАВИЛО, КОТОРОЕ ИЗ ЭТОГО СЛЕДУЕТ</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Длинное простое предложение лучше короткого свёрнутого</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Существительные вместо глаголов («перенос, заморозка, замена») читаются тяжело — нужны глаголы и вопросы целиком</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>«в статьях про КИТАЙСКОМ ЯЗЫКЕ для детей»</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>«в статьях про китайский язык для детей»</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>СЛОМАННЫЙ ПАДЕЖ. Заведён отдельный вариант подписи в винительном</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>«в разборе про ГРУППОВЫХ ЗАНЯТИЯХ по китайскому языку»</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>«в разборе про групповые занятия по китайскому языку»</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>СЛОМАННЫЙ ПАДЕЖ. Заведён отдельный вариант подписи в винительном</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Проверка на метафоры</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Пройдена</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Метафор на месте обычных глаголов нет. Слово «спотыкаются» в тексте отсутствует — проверено отдельным поиском</t>
         </is>
@@ -1531,7 +1701,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>37 194 знака</t>
+          <t>37 497 знаков</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1713,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>0 (ёлочек 7 / 7)</t>
+          <t>0 (ёлочек 4 / 4)</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1725,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Инфографика 26,1 %, «Из личного опыта» 35,9 %, FAQ 59,2 %</t>
+          <t>Инфографика 26,6 %, «Из личного опыта» 36,7 %, FAQ 59,4 %</t>
         </is>
       </c>
     </row>
@@ -1959,7 +2129,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>«ДВЕРИ-В-ДВЕРЬ»</t>
+          <t>ДОРОГА КАК ПРИЧИНА БРОСИТЬ</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -2004,7 +2174,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Кому офлайн ПРАВДА нужнее</t>
+          <t>Кому очные занятия ПРАВДА нужнее</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -2097,7 +2267,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Человек, который ищет школу в Москве, получает то, чего ему действительно не хватает: способ посчитать полную цену занятия вместе с дорогой и понять, нужен ли ему офлайн вообще</t>
+          <t>Человек, который ищет школу в Москве, получает то, чего ему действительно не хватает: способ посчитать, сколько времени на самом деле займёт один урок, и понять, нужны ли ему очные занятия вообще</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2279,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Платите вы не за час, а за вечер. Регулярность рушит дорога, а не сложность языка</t>
+          <t>Платите вы не за час, а за вечер. Бросают из-за дороги, а не из-за того, что язык сложный</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2402,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Время двери-в-дверь; кому офлайн правда нужнее; перенос, заморозка и замена преподавателя; признание, что офиса в Москве нет</t>
+          <t>Как посчитать время вместе с дорогой; кому очные занятия правда нужнее; три вопроса про расписание; признание, что офиса в Москве нет</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2249,12 +2419,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Написан заново</t>
+          <t>Написан заново, потом укорочен</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Было: «Как выбрать сильную школу китайского языка в Москве и не пожалеть». Ключ не в начале, «сильную» и «не пожалеть» — оценки без содержания, и ровно такой заголовок уже отработан разделом на лендинге</t>
+          <t>Было: «Как выбрать сильную школу китайского языка в Москве и не пожалеть». Ключ не в начале, «сильную» и «не пожалеть» — оценки без содержания, и такой заголовок уже отработан разделом на лендинге. После первой сдачи укорочен ещё раз: «что считать перед выбором, кроме цены занятия» читалось тяжело</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2485,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Раздел 2 (маленький ребёнок — один из трёх случаев за офлайн) + ссылки на детские статьи</t>
+          <t>Раздел 2 (ребёнку мало лет — один из трёх случаев за очные занятия) + ссылки на детские статьи</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2586,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Считайте не цену занятия, а время двери-в-дверь</t>
+          <t>Считайте не цену занятия, а время вместе с дорогой</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2431,7 +2601,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Кому офлайн правда нужнее</t>
+          <t>Кому очные занятия правда нужнее</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2446,12 +2616,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Три вопроса про расписание, которых нет в обычных списках</t>
+          <t>Три вопроса про расписание, которые задают редко</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Перенос, заморозка, замена преподавателя — то, что решает, дойдёте ли вы до конца года</t>
+          <t>Можно ли перенести занятие, что будет с оплатой при отъезде, кто заменит заболевшего преподавателя</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2678,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ПОЗИЦИИ ПРАВИЛИ ОДИН РАЗ</t>
+          <t>ПОЗИЦИИ ПРАВИЛИ ДВАЖДЫ</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Сначала инфографика стояла на 14,3 % — слишком рано, первый раздел короткий. Картинку перенесли в конец первого раздела, историю — в концовку второго. Стало 26,1 % и 35,9 %</t>
+          <t>Сначала инфографика стояла на 14,3 % — слишком рано, первый раздел короткий. Картинку перенесли в конец первого раздела, историю — в концовку второго. После правки языка картинка съехала на 25,9 %, перед ней добавили одну полезную строку. Стало 26,6 % и 36,7 %</t>
         </is>
       </c>
     </row>
